--- a/public/sample_import_data/job_postings.xlsx
+++ b/public/sample_import_data/job_postings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\visibleone\projects\example-app\public\sample_import_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3858C5A-A21E-4F74-9212-1EC28848E13B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84D976F8-B57C-42C6-A580-31CC09E17149}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,29 +20,179 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Software Development</t>
-  </si>
-  <si>
-    <t>Software Development and Management</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+  <si>
+    <t>Company</t>
+  </si>
+  <si>
+    <t>Department</t>
+  </si>
+  <si>
+    <t>Designation</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Experience Level</t>
+  </si>
+  <si>
+    <t>Job Function</t>
+  </si>
+  <si>
+    <t>Min Education Level</t>
+  </si>
+  <si>
+    <t>Summary</t>
+  </si>
+  <si>
+    <t>Open To</t>
+  </si>
+  <si>
+    <t>Male/Female</t>
+  </si>
+  <si>
+    <t>Roles And Responsibilities</t>
+  </si>
+  <si>
+    <t>Requirements</t>
+  </si>
+  <si>
+    <t>What We Can Offer Benefits</t>
+  </si>
+  <si>
+    <t>What We Can Offer Highlights</t>
+  </si>
+  <si>
+    <t>What We Can Offer Career Opportunities</t>
+  </si>
+  <si>
+    <t>Job Type</t>
+  </si>
+  <si>
+    <t>Full-Time</t>
+  </si>
+  <si>
+    <t>Work Arrangement</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>Skills</t>
+  </si>
+  <si>
+    <t>PHP, Laravel</t>
+  </si>
+  <si>
+    <t>Salary Type</t>
+  </si>
+  <si>
+    <t>Range</t>
+  </si>
+  <si>
+    <t>MMK</t>
+  </si>
+  <si>
+    <t>Salary Notes</t>
+  </si>
+  <si>
+    <t>Salary Amount</t>
+  </si>
+  <si>
+    <t>Min Salary</t>
+  </si>
+  <si>
+    <t>Max Salary</t>
+  </si>
+  <si>
+    <t>vacancies</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>Published At</t>
+  </si>
+  <si>
+    <t>Deadline Date</t>
+  </si>
+  <si>
+    <t>Published</t>
+  </si>
+  <si>
+    <t>Depend On Experience</t>
+  </si>
+  <si>
+    <t>YGN</t>
+  </si>
+  <si>
+    <t>On-Site</t>
+  </si>
+  <si>
+    <t>Design, build, and maintain efficient, reusable, and reliable PHP code.</t>
+  </si>
+  <si>
+    <t>Design, Code, Review, Mentor.</t>
+  </si>
+  <si>
+    <t>5+ years Laravel, solid MySQL, AWS experience.</t>
+  </si>
+  <si>
+    <t>Health insurance, annual bonuses.</t>
+  </si>
+  <si>
+    <t>Work with a great team on exciting projects.</t>
+  </si>
+  <si>
+    <t>Pathway to Principal Engineer.</t>
+  </si>
+  <si>
+    <t>Example Corp</t>
+  </si>
+  <si>
+    <t>Human Resources</t>
+  </si>
+  <si>
+    <t>Team Lead</t>
+  </si>
+  <si>
+    <t>Team Leader</t>
+  </si>
+  <si>
+    <t>Associate</t>
+  </si>
+  <si>
+    <t>Administrative</t>
+  </si>
+  <si>
+    <t>Associate Degree</t>
+  </si>
+  <si>
+    <t>Currency Code</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFCE9178"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -65,8 +215,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -371,30 +526,214 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:AB2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.88671875" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.21875" customWidth="1"/>
+    <col min="5" max="5" width="16.88671875" customWidth="1"/>
+    <col min="6" max="6" width="23" customWidth="1"/>
+    <col min="7" max="7" width="18.33203125" customWidth="1"/>
+    <col min="9" max="9" width="12.33203125" customWidth="1"/>
+    <col min="10" max="10" width="23.88671875" customWidth="1"/>
+    <col min="11" max="11" width="12.21875" customWidth="1"/>
+    <col min="12" max="12" width="24.21875" customWidth="1"/>
+    <col min="13" max="13" width="25.21875" customWidth="1"/>
+    <col min="14" max="14" width="33.88671875" customWidth="1"/>
+    <col min="16" max="16" width="17.44140625" customWidth="1"/>
+    <col min="19" max="19" width="11.77734375" customWidth="1"/>
+    <col min="22" max="22" width="14.109375" customWidth="1"/>
+    <col min="27" max="28" width="10.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N1" t="s">
+        <v>14</v>
+      </c>
+      <c r="O1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P1" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>18</v>
+      </c>
+      <c r="R1" t="s">
+        <v>19</v>
+      </c>
+      <c r="S1" t="s">
+        <v>21</v>
+      </c>
+      <c r="T1" t="s">
+        <v>49</v>
+      </c>
+      <c r="U1" t="s">
+        <v>24</v>
+      </c>
+      <c r="V1" t="s">
+        <v>25</v>
+      </c>
+      <c r="W1" t="s">
+        <v>26</v>
+      </c>
+      <c r="X1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="I2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="O2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>34</v>
+      </c>
+      <c r="R2" t="s">
+        <v>20</v>
+      </c>
+      <c r="S2" t="s">
+        <v>22</v>
+      </c>
+      <c r="T2" t="s">
+        <v>23</v>
+      </c>
+      <c r="U2" t="s">
+        <v>33</v>
+      </c>
+      <c r="W2">
+        <v>100000</v>
+      </c>
+      <c r="X2">
+        <v>200000</v>
+      </c>
+      <c r="Y2">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
-        <v>3</v>
+      <c r="Z2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA2" s="1">
+        <v>45954</v>
+      </c>
+      <c r="AB2" s="1">
+        <v>45960</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="5">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2" xr:uid="{33FEE9E3-2E7C-4327-AEC8-A29B0A971F22}">
+      <formula1>"Male/Female, Male, Female"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2" xr:uid="{882FFB28-8240-43E7-98EF-17E18D9B0766}">
+      <formula1>"Full-Time, Part-Time, Contract, Internship"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2" xr:uid="{BBE9CDC0-603E-4D1E-986C-452471F1B79B}">
+      <formula1>"Range, Up_To, Around, Fixed, Negotiable"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z2" xr:uid="{11931815-6BE7-43B7-BE4A-400DDB8DB1E4}">
+      <formula1>"Draft, Published, Closed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2" xr:uid="{23F4DBFF-8CC3-41C6-9F12-333F5DFCB6C8}">
+      <formula1>"Remote, Hybrid, On-Site"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>